--- a/EfficiencyTimesAndData2.xlsx
+++ b/EfficiencyTimesAndData2.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u5711834\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9C4943-1269-4DEB-8F8D-6F6FC55258D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6143F5AF-038C-400C-B3CB-4FD80014E9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5BD5D07B-CEB2-477E-82C7-A8899E6CC13F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="45">
   <si>
     <t>Initial Test</t>
   </si>
@@ -65,13 +66,7 @@
     <t>Pre-calculated Barycentrics</t>
   </si>
   <si>
-    <t>Causes small tearing artefacts?</t>
-  </si>
-  <si>
     <t>Line optimized</t>
-  </si>
-  <si>
-    <t>Causes more artefacts, ignoring 0 triangles now crashes</t>
   </si>
   <si>
     <t>Speedup</t>
@@ -89,178 +84,94 @@
     <t>Alt Sc. 3</t>
   </si>
   <si>
-    <t>Optim. 2</t>
-  </si>
-  <si>
     <t>Draw Optimisations</t>
   </si>
   <si>
-    <t>Optim. 3</t>
+    <t>2 Threads</t>
   </si>
   <si>
-    <t>2 Bad Threads</t>
+    <t>4 Threads</t>
   </si>
   <si>
-    <t>4 Bad Threads</t>
+    <t>11 Threads</t>
   </si>
   <si>
-    <t>11 Bad Threads</t>
+    <t>22 Threads</t>
   </si>
   <si>
-    <t>22 Bad Threads</t>
+    <t>3 Threads</t>
   </si>
   <si>
-    <t>1 :583.728ms</t>
+    <t>5 Threads</t>
   </si>
   <si>
-    <t>2 :491.526ms</t>
+    <t>6 Threads</t>
   </si>
   <si>
-    <t>3 :353.156ms</t>
+    <t>7 Threads</t>
   </si>
   <si>
-    <t>4 :365.734ms</t>
+    <t>8 Threads</t>
   </si>
   <si>
-    <t>5 :349.3ms</t>
+    <t>14 Threads</t>
   </si>
   <si>
-    <t>6 :401.815ms</t>
+    <t>18 Threads</t>
   </si>
   <si>
-    <t>7 :390.015ms</t>
+    <t>Final Time</t>
   </si>
   <si>
-    <t>8 :386.725ms</t>
+    <t>1 :9231.5ms</t>
   </si>
   <si>
-    <t>9 :396.019ms</t>
+    <t>2 :9590.01ms</t>
   </si>
   <si>
-    <t>10 :394.116ms</t>
+    <t>3 :10040ms</t>
   </si>
   <si>
-    <t>11 :418.629ms</t>
+    <t>4 :10117.3ms</t>
   </si>
   <si>
-    <t>12 :380.41ms</t>
+    <t>5 :10119.6ms</t>
   </si>
   <si>
-    <t>13 :404.764ms</t>
+    <t>6 :10168.6ms</t>
   </si>
   <si>
-    <t>14 :410.329ms</t>
+    <t>7 :10169.3ms</t>
   </si>
   <si>
-    <t>15 :447.186ms</t>
+    <t>8 :10257.2ms</t>
   </si>
   <si>
-    <t>16 :400.7ms</t>
+    <t>9 :10368.4ms</t>
   </si>
   <si>
-    <t>17 :390.067ms</t>
+    <t>10 :10401.8ms</t>
   </si>
   <si>
-    <t>18 :384.273ms</t>
+    <t>11 :10410ms</t>
   </si>
   <si>
-    <t>19 :401.104ms</t>
+    <t>12 :10438.7ms</t>
   </si>
   <si>
-    <t>20 :396.471ms</t>
+    <t>13 :10430.9ms</t>
   </si>
   <si>
-    <t>21 :445.969ms</t>
+    <t>14 :10481.2ms</t>
   </si>
   <si>
-    <t>22 :382.006ms</t>
+    <t>15 :10441.5ms</t>
   </si>
   <si>
-    <t>23 :436.437ms</t>
+    <t>16 :10487.2ms</t>
   </si>
   <si>
-    <t>24 :422.005ms</t>
-  </si>
-  <si>
-    <t>25 :404.941ms</t>
-  </si>
-  <si>
-    <t>26 :382.329ms</t>
-  </si>
-  <si>
-    <t>27 :364.404ms</t>
-  </si>
-  <si>
-    <t>28 :365.247ms</t>
-  </si>
-  <si>
-    <t>29 :378.696ms</t>
-  </si>
-  <si>
-    <t>30 :360.766ms</t>
-  </si>
-  <si>
-    <t>31 :367.267ms</t>
-  </si>
-  <si>
-    <t>32 :382.697ms</t>
-  </si>
-  <si>
-    <t>33 :345.573ms</t>
-  </si>
-  <si>
-    <t>34 :345.134ms</t>
-  </si>
-  <si>
-    <t>35 :347.737ms</t>
-  </si>
-  <si>
-    <t>36 :368.545ms</t>
-  </si>
-  <si>
-    <t>37 :347.236ms</t>
-  </si>
-  <si>
-    <t>38 :332.801ms</t>
-  </si>
-  <si>
-    <t>39 :349.448ms</t>
-  </si>
-  <si>
-    <t>40 :352.241ms</t>
-  </si>
-  <si>
-    <t>41 :361.844ms</t>
-  </si>
-  <si>
-    <t>42 :379.24ms</t>
-  </si>
-  <si>
-    <t>43 :391.984ms</t>
-  </si>
-  <si>
-    <t>44 :371.899ms</t>
-  </si>
-  <si>
-    <t>45 :396.377ms</t>
-  </si>
-  <si>
-    <t>46 :373.417ms</t>
-  </si>
-  <si>
-    <t>47 :355.076ms</t>
-  </si>
-  <si>
-    <t>48 :394.252ms</t>
-  </si>
-  <si>
-    <t>49 :425.755ms</t>
-  </si>
-  <si>
-    <t>50 :446.433ms</t>
-  </si>
-  <si>
-    <t>51 :481.124ms</t>
+    <t>Final Test</t>
   </si>
 </sst>
 </file>
@@ -322,26 +233,15 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="medium">
+      <right style="medium">
         <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -367,6 +267,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -382,6 +293,19 @@
     <border>
       <left/>
       <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -453,43 +377,32 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,6 +419,1448 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Concurrency Speedup</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scene 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="x"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet2!$A$17:$A$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet2!$B$17:$B$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.4886725788212187E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.11870971578567402</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2.5673305831682702E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.8406210243939292E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.9379179970767932E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-8.4128421913055473E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-7.7078698975804327E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.23721628194995847</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.23172290063455536</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.36598854766960831</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.46991872933011025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0F56-43B7-9D98-D78D7C64B31D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$C$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scene 2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="x"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet2!$A$17:$A$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet2!$C$17:$C$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.16901679824847293</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.43914575712744286</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.69615852953223567</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.82948711569806344</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.87589678327071052</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.79643092218730782</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.64437679586965135</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.75367943382890967</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.52937293756965342</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.35001375449327288</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.19741982740591402</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0F56-43B7-9D98-D78D7C64B31D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$D$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scene 3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="x"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet2!$A$17:$A$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet2!$D$17:$D$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1437018228503486</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.12608958421686767</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.22741246740267096</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.3544424378171334E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.2084773277516927E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6418950030046009E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.2012849013390214E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.4987845350786824E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1.9188354446108669E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.3087439849795768E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-6.4548855608117406E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0F56-43B7-9D98-D78D7C64B31D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1330210704"/>
+        <c:axId val="1362724576"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1330210704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="22"/>
+          <c:min val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Number</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-GB" baseline="0"/>
+                  <a:t> of Threads</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.44559614176858597"/>
+              <c:y val="0.86971088651977491"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1362724576"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1362724576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Speedup</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1330210704"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>26670</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEBD025E-E348-6986-C739-0D7645627A1E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -825,17 +2180,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68CE1711-1BB8-4589-A8C0-E797B318A73C}">
-  <dimension ref="A1:T116"/>
+  <dimension ref="A1:V116"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.44140625" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8" customWidth="1"/>
     <col min="15" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -845,7 +2200,7 @@
     <col min="21" max="21" width="9.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -853,25 +2208,49 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="N1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -888,28 +2267,48 @@
         <v>2.144571</v>
       </c>
       <c r="F2" s="2">
-        <v>2.0765880000000001</v>
+        <v>2.0329869999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>2.109772</v>
-      </c>
-      <c r="H2" s="2"/>
+        <v>1.9170039999999999</v>
+      </c>
+      <c r="H2" s="2">
+        <v>2.2010800000000001</v>
+      </c>
       <c r="I2" s="2">
-        <v>3.4989659999999998</v>
-      </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
+        <v>2.1058110000000001</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1.986856</v>
+      </c>
+      <c r="K2" s="2">
+        <v>2.3415629999999998</v>
+      </c>
+      <c r="L2" s="2">
+        <v>2.323677</v>
+      </c>
+      <c r="M2" s="2">
+        <v>2.8115060000000001</v>
+      </c>
+      <c r="N2" s="2">
+        <v>2.7914029999999999</v>
+      </c>
+      <c r="O2" s="2">
+        <v>3.3825430000000001</v>
+      </c>
+      <c r="P2" s="2">
+        <v>4.0457400000000003</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>1.9870000000000001</v>
+      </c>
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -926,30 +2325,48 @@
         <v>0.73171379999999997</v>
       </c>
       <c r="F3" s="2">
-        <v>0.62990590000000002</v>
+        <v>0.62592239999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>0.41465239999999998</v>
+        <v>0.5084362</v>
       </c>
       <c r="H3" s="2">
-        <v>0.46664149999999999</v>
+        <v>0.43139470000000002</v>
       </c>
       <c r="I3" s="2">
-        <v>0.70142590000000005</v>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
+        <v>0.39995570000000003</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.39006079999999999</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.40731529999999999</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0.44497940000000002</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0.41724489999999997</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0.47844039999999999</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0.54200470000000001</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0.61107540000000005</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0.39</v>
+      </c>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -966,26 +2383,50 @@
         <v>10.419269999999999</v>
       </c>
       <c r="F4" s="2">
-        <v>9.0070929999999993</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
+        <v>9.1101279999999996</v>
+      </c>
+      <c r="G4" s="2">
+        <v>9.2526119999999992</v>
+      </c>
+      <c r="H4" s="2">
+        <v>8.4888089999999998</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9.6159140000000001</v>
+      </c>
+      <c r="J4" s="2">
+        <v>9.9034510000000004</v>
+      </c>
+      <c r="K4" s="2">
+        <v>10.250959999999999</v>
+      </c>
+      <c r="L4" s="2">
+        <v>9.8108699999999995</v>
+      </c>
+      <c r="M4" s="2">
+        <v>10.36229</v>
+      </c>
+      <c r="N4" s="2">
+        <v>10.62311</v>
+      </c>
+      <c r="O4" s="2">
+        <v>10.28467</v>
+      </c>
+      <c r="P4" s="2">
+        <v>11.13823</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>8.4890000000000008</v>
+      </c>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2">
         <v>13.098000000000001</v>
@@ -1002,10 +2443,10 @@
       <c r="F5" s="2">
         <v>10.525869999999999</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2">
         <v>10.69753</v>
       </c>
-      <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1014,20 +2455,16 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
+      <c r="Q5" s="2">
+        <v>10.26145</v>
+      </c>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1035,273 +2472,273 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="G8" t="s">
         <v>7</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="L9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <f>_xlfn.NUMBERVALUE(IFERROR(RIGHT(LEFT(A12, LEN(A12)-2), LEN(A12)-5), ""))</f>
-        <v>583.72799999999995</v>
+        <v>9231.5</v>
       </c>
       <c r="E12">
         <f>IF(D12=0, "", D12)</f>
-        <v>583.72799999999995</v>
+        <v>9231.5</v>
       </c>
       <c r="G12">
         <f>AVERAGE(E13:E101)</f>
-        <v>388.4243800000001</v>
+        <v>10261.447333333334</v>
       </c>
       <c r="H12">
         <f>MEDIAN(E13:E101)</f>
-        <v>383.48500000000001</v>
+        <v>10368.4</v>
       </c>
       <c r="I12">
         <f>MIN(E13:E101)</f>
-        <v>332.80099999999999</v>
+        <v>9590.01</v>
       </c>
       <c r="J12">
         <f>MAX(E13:E101)</f>
-        <v>491.52600000000001</v>
+        <v>10487.2</v>
       </c>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <f t="shared" ref="D13:D20" si="0">_xlfn.NUMBERVALUE(IFERROR(RIGHT(LEFT(A13, LEN(A13)-2), LEN(A13)-5), ""))</f>
-        <v>491.52600000000001</v>
+        <v>9590.01</v>
       </c>
       <c r="E13">
         <f t="shared" ref="E13:E76" si="1">IF(D13=0, "", D13)</f>
-        <v>491.52600000000001</v>
+        <v>9590.01</v>
       </c>
       <c r="H13">
         <f>H12/G12</f>
-        <v>0.98728354795854967</v>
+        <v>1.0104227662231662</v>
       </c>
       <c r="I13">
         <f>I12/G12</f>
-        <v>0.85679740288186834</v>
+        <v>0.9345669951301866</v>
       </c>
       <c r="J13">
         <f>J12/G12</f>
-        <v>1.2654355012422234</v>
+        <v>1.0220000804304994</v>
       </c>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>353.15600000000001</v>
+        <v>10040</v>
       </c>
       <c r="E14">
         <f t="shared" si="1"/>
-        <v>353.15600000000001</v>
+        <v>10040</v>
       </c>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D15">
         <f t="shared" si="0"/>
-        <v>365.73399999999998</v>
+        <v>10117.299999999999</v>
       </c>
       <c r="E15">
         <f t="shared" si="1"/>
-        <v>365.73399999999998</v>
+        <v>10117.299999999999</v>
       </c>
       <c r="L15" s="1"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="R15" s="9" t="s">
+      <c r="O15" s="17"/>
+      <c r="P15" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="R15" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D16">
         <f t="shared" si="0"/>
-        <v>349.3</v>
+        <v>10119.6</v>
       </c>
       <c r="E16">
         <f t="shared" si="1"/>
-        <v>349.3</v>
+        <v>10119.6</v>
       </c>
       <c r="L16" s="1"/>
-      <c r="O16" s="7" t="s">
+      <c r="O16" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="P16" s="12">
+      <c r="P16" s="15">
         <v>4.6647999999999996</v>
       </c>
       <c r="Q16" s="3">
         <v>4.8478880000000002</v>
       </c>
-      <c r="R16" s="10">
+      <c r="R16" s="13">
         <f>ABS(P16/Q16-1)</f>
         <v>3.776654906218968E-2</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <f t="shared" si="0"/>
-        <v>401.815</v>
+        <v>10168.6</v>
       </c>
       <c r="E17">
         <f t="shared" si="1"/>
-        <v>401.815</v>
+        <v>10168.6</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
-      <c r="O17" s="7" t="s">
+      <c r="O17" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="P17" s="12">
+      <c r="P17" s="15">
         <v>1.827099</v>
       </c>
       <c r="Q17" s="3">
         <v>1.8707020000000001</v>
       </c>
-      <c r="R17" s="10">
+      <c r="R17" s="13">
         <f t="shared" ref="R17:R18" si="2">ABS(P17/Q17-1)</f>
         <v>2.3308362315323405E-2</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D18">
         <f t="shared" si="0"/>
-        <v>390.01499999999999</v>
+        <v>10169.299999999999</v>
       </c>
       <c r="E18">
         <f t="shared" si="1"/>
-        <v>390.01499999999999</v>
-      </c>
-      <c r="J18" s="14"/>
-      <c r="K18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>19</v>
+        <v>10169.299999999999</v>
+      </c>
+      <c r="J18" s="17"/>
+      <c r="K18" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="O18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="O18" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="13">
+      <c r="P18" s="16">
         <v>11.00719</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="Q18" s="5">
         <v>13.098000000000001</v>
       </c>
-      <c r="R18" s="11">
+      <c r="R18" s="14">
         <f t="shared" si="2"/>
         <v>0.15962818750954355</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D19">
         <f t="shared" si="0"/>
-        <v>386.72500000000002</v>
+        <v>10257.200000000001</v>
       </c>
       <c r="E19">
         <f t="shared" si="1"/>
-        <v>386.72500000000002</v>
-      </c>
-      <c r="J19" s="7" t="s">
+        <v>10257.200000000001</v>
+      </c>
+      <c r="J19" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="K19" s="15">
-        <v>2.5230709999999998</v>
-      </c>
-      <c r="L19" s="16">
-        <v>2.144571</v>
-      </c>
-      <c r="M19" s="17">
+      <c r="K19" s="3">
+        <v>4.6647999999999996</v>
+      </c>
+      <c r="L19" s="18">
+        <v>1.9870000000000001</v>
+      </c>
+      <c r="M19" s="4">
         <f>K19/L19-1</f>
-        <v>0.17649217489185465</v>
-      </c>
-      <c r="O19" s="14"/>
-      <c r="P19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="R19" s="9" t="s">
+        <v>1.3476597886260691</v>
+      </c>
+      <c r="O19" s="17"/>
+      <c r="P19" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q19" s="8" t="s">
         <v>13</v>
+      </c>
+      <c r="R19" s="12" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D20">
         <f t="shared" si="0"/>
-        <v>396.01900000000001</v>
+        <v>10368.4</v>
       </c>
       <c r="E20">
         <f t="shared" si="1"/>
-        <v>396.01900000000001</v>
-      </c>
-      <c r="J20" s="7" t="s">
+        <v>10368.4</v>
+      </c>
+      <c r="J20" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="K20" s="12">
-        <v>0.87321459999999995</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0.73171379999999997</v>
-      </c>
-      <c r="M20" s="10">
+      <c r="K20" s="3">
+        <v>1.827099</v>
+      </c>
+      <c r="L20" s="18">
+        <v>0.39</v>
+      </c>
+      <c r="M20" s="4">
         <f t="shared" ref="M20:M22" si="3">K20/L20-1</f>
-        <v>0.19338271329582679</v>
-      </c>
-      <c r="O20" s="7" t="s">
+        <v>3.6848692307692303</v>
+      </c>
+      <c r="O20" s="10" t="s">
         <v>1</v>
       </c>
       <c r="P20" s="3">
@@ -1310,37 +2747,37 @@
       <c r="Q20" s="3">
         <v>3.1094059999999999</v>
       </c>
-      <c r="R20" s="10">
+      <c r="R20" s="13">
         <f>ABS(P20/Q20-1)</f>
         <v>2.1798697243139098E-2</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D21">
         <f>_xlfn.NUMBERVALUE(IFERROR(RIGHT(LEFT(A21, LEN(A21)-2), LEN(A21)-6), ""))</f>
-        <v>394.11599999999999</v>
+        <v>10401.799999999999</v>
       </c>
       <c r="E21">
         <f t="shared" si="1"/>
-        <v>394.11599999999999</v>
-      </c>
-      <c r="J21" s="7" t="s">
+        <v>10401.799999999999</v>
+      </c>
+      <c r="J21" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="12">
-        <v>10.67651</v>
-      </c>
-      <c r="L21" s="3">
-        <v>10.419269999999999</v>
-      </c>
-      <c r="M21" s="10">
+      <c r="K21" s="3">
+        <v>11.00719</v>
+      </c>
+      <c r="L21" s="18">
+        <v>8.4890000000000008</v>
+      </c>
+      <c r="M21" s="4">
         <f t="shared" si="3"/>
-        <v>2.4688869757670373E-2</v>
-      </c>
-      <c r="O21" s="7" t="s">
+        <v>0.29664153610554811</v>
+      </c>
+      <c r="O21" s="10" t="s">
         <v>2</v>
       </c>
       <c r="P21" s="3">
@@ -1349,591 +2786,486 @@
       <c r="Q21" s="3">
         <v>1.1140140000000001</v>
       </c>
-      <c r="R21" s="10">
+      <c r="R21" s="13">
         <f t="shared" ref="R21:R22" si="4">ABS(P21/Q21-1)</f>
         <v>2.9501424578147306E-2</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D22">
         <f t="shared" ref="D22:D85" si="5">_xlfn.NUMBERVALUE(IFERROR(RIGHT(LEFT(A22, LEN(A22)-2), LEN(A22)-6), ""))</f>
-        <v>418.62900000000002</v>
+        <v>10410</v>
       </c>
       <c r="E22">
         <f t="shared" si="1"/>
-        <v>418.62900000000002</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K22" s="13">
-        <v>12.218629999999999</v>
-      </c>
-      <c r="L22" s="4">
-        <v>12.01618</v>
-      </c>
-      <c r="M22" s="11">
+        <v>10410</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K22" s="5">
+        <v>13.098000000000001</v>
+      </c>
+      <c r="L22" s="19">
+        <v>10.26145</v>
+      </c>
+      <c r="M22" s="6">
         <f t="shared" si="3"/>
-        <v>1.6848116456311235E-2</v>
-      </c>
-      <c r="O22" s="8" t="s">
+        <v>0.27642779529208839</v>
+      </c>
+      <c r="O22" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="4">
+      <c r="P22" s="5">
         <v>10.142440000000001</v>
       </c>
-      <c r="Q22" s="4">
+      <c r="Q22" s="5">
         <v>12.29393</v>
       </c>
-      <c r="R22" s="11">
+      <c r="R22" s="14">
         <f t="shared" si="4"/>
         <v>0.1750042500648693</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D23">
         <f t="shared" si="5"/>
-        <v>380.41</v>
+        <v>10438.700000000001</v>
       </c>
       <c r="E23">
         <f t="shared" si="1"/>
-        <v>380.41</v>
+        <v>10438.700000000001</v>
       </c>
       <c r="L23" s="1"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D24">
         <f t="shared" si="5"/>
-        <v>404.76400000000001</v>
+        <v>10430.9</v>
       </c>
       <c r="E24">
         <f t="shared" si="1"/>
-        <v>404.76400000000001</v>
+        <v>10430.9</v>
       </c>
       <c r="L24" s="1"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D25">
         <f t="shared" si="5"/>
-        <v>410.32900000000001</v>
+        <v>10481.200000000001</v>
       </c>
       <c r="E25">
         <f t="shared" si="1"/>
-        <v>410.32900000000001</v>
+        <v>10481.200000000001</v>
       </c>
       <c r="L25" s="1"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D26">
         <f t="shared" si="5"/>
-        <v>447.18599999999998</v>
+        <v>10441.5</v>
       </c>
       <c r="E26">
         <f t="shared" si="1"/>
-        <v>447.18599999999998</v>
+        <v>10441.5</v>
       </c>
       <c r="L26" s="1"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D27">
         <f t="shared" si="5"/>
-        <v>400.7</v>
+        <v>10487.2</v>
       </c>
       <c r="E27">
         <f t="shared" si="1"/>
-        <v>400.7</v>
+        <v>10487.2</v>
       </c>
       <c r="L27" s="1"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>40</v>
-      </c>
       <c r="D28">
         <f t="shared" si="5"/>
-        <v>390.06700000000001</v>
-      </c>
-      <c r="E28">
-        <f t="shared" si="1"/>
-        <v>390.06700000000001</v>
+        <v>0</v>
+      </c>
+      <c r="E28" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="L28" s="1"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>41</v>
-      </c>
       <c r="D29">
         <f t="shared" si="5"/>
-        <v>384.27300000000002</v>
-      </c>
-      <c r="E29">
-        <f t="shared" si="1"/>
-        <v>384.27300000000002</v>
+        <v>0</v>
+      </c>
+      <c r="E29" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="L29" s="1"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>42</v>
-      </c>
       <c r="D30">
         <f t="shared" si="5"/>
-        <v>401.10399999999998</v>
-      </c>
-      <c r="E30">
-        <f t="shared" si="1"/>
-        <v>401.10399999999998</v>
+        <v>0</v>
+      </c>
+      <c r="E30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="L30" s="1"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>43</v>
-      </c>
       <c r="D31">
         <f t="shared" si="5"/>
-        <v>396.471</v>
-      </c>
-      <c r="E31">
-        <f t="shared" si="1"/>
-        <v>396.471</v>
+        <v>0</v>
+      </c>
+      <c r="E31" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="L31" s="1"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>44</v>
-      </c>
       <c r="D32">
         <f t="shared" si="5"/>
-        <v>445.96899999999999</v>
-      </c>
-      <c r="E32">
-        <f t="shared" si="1"/>
-        <v>445.96899999999999</v>
+        <v>0</v>
+      </c>
+      <c r="E32" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>45</v>
-      </c>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33">
         <f t="shared" si="5"/>
-        <v>382.00599999999997</v>
-      </c>
-      <c r="E33">
-        <f t="shared" si="1"/>
-        <v>382.00599999999997</v>
+        <v>0</v>
+      </c>
+      <c r="E33" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>46</v>
-      </c>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34">
         <f t="shared" si="5"/>
-        <v>436.43700000000001</v>
-      </c>
-      <c r="E34">
-        <f t="shared" si="1"/>
-        <v>436.43700000000001</v>
+        <v>0</v>
+      </c>
+      <c r="E34" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>47</v>
-      </c>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35">
         <f t="shared" si="5"/>
-        <v>422.005</v>
-      </c>
-      <c r="E35">
-        <f t="shared" si="1"/>
-        <v>422.005</v>
+        <v>0</v>
+      </c>
+      <c r="E35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>48</v>
-      </c>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36">
         <f t="shared" si="5"/>
-        <v>404.94099999999997</v>
-      </c>
-      <c r="E36">
-        <f t="shared" si="1"/>
-        <v>404.94099999999997</v>
+        <v>0</v>
+      </c>
+      <c r="E36" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="L36" s="1"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>49</v>
-      </c>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37">
         <f t="shared" si="5"/>
-        <v>382.32900000000001</v>
-      </c>
-      <c r="E37">
-        <f t="shared" si="1"/>
-        <v>382.32900000000001</v>
+        <v>0</v>
+      </c>
+      <c r="E37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="L37" s="1"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>50</v>
-      </c>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38">
         <f t="shared" si="5"/>
-        <v>364.404</v>
-      </c>
-      <c r="E38">
-        <f t="shared" si="1"/>
-        <v>364.404</v>
+        <v>0</v>
+      </c>
+      <c r="E38" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="L38" s="1"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>51</v>
-      </c>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39">
         <f t="shared" si="5"/>
-        <v>365.24700000000001</v>
-      </c>
-      <c r="E39">
-        <f t="shared" si="1"/>
-        <v>365.24700000000001</v>
+        <v>0</v>
+      </c>
+      <c r="E39" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="L39" s="1"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>52</v>
-      </c>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40">
         <f t="shared" si="5"/>
-        <v>378.69600000000003</v>
-      </c>
-      <c r="E40">
-        <f t="shared" si="1"/>
-        <v>378.69600000000003</v>
+        <v>0</v>
+      </c>
+      <c r="E40" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="L40" s="1"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>53</v>
-      </c>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41">
         <f t="shared" si="5"/>
-        <v>360.76600000000002</v>
-      </c>
-      <c r="E41">
-        <f t="shared" si="1"/>
-        <v>360.76600000000002</v>
+        <v>0</v>
+      </c>
+      <c r="E41" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>54</v>
-      </c>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42">
         <f t="shared" si="5"/>
-        <v>367.267</v>
-      </c>
-      <c r="E42">
-        <f t="shared" si="1"/>
-        <v>367.267</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>55</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E42" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43">
         <f t="shared" si="5"/>
-        <v>382.697</v>
-      </c>
-      <c r="E43">
-        <f t="shared" si="1"/>
-        <v>382.697</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>56</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E43" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44">
         <f t="shared" si="5"/>
-        <v>345.57299999999998</v>
-      </c>
-      <c r="E44">
-        <f t="shared" si="1"/>
-        <v>345.57299999999998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>57</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E44" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45">
         <f t="shared" si="5"/>
-        <v>345.13400000000001</v>
-      </c>
-      <c r="E45">
-        <f t="shared" si="1"/>
-        <v>345.13400000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>58</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E45" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46">
         <f t="shared" si="5"/>
-        <v>347.73700000000002</v>
-      </c>
-      <c r="E46">
-        <f t="shared" si="1"/>
-        <v>347.73700000000002</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>59</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E46" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D47">
         <f t="shared" si="5"/>
-        <v>368.54500000000002</v>
-      </c>
-      <c r="E47">
-        <f t="shared" si="1"/>
-        <v>368.54500000000002</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>60</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E47" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48">
         <f t="shared" si="5"/>
-        <v>347.23599999999999</v>
-      </c>
-      <c r="E48">
-        <f t="shared" si="1"/>
-        <v>347.23599999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>61</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E48" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D49">
         <f t="shared" si="5"/>
-        <v>332.80099999999999</v>
-      </c>
-      <c r="E49">
-        <f t="shared" si="1"/>
-        <v>332.80099999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>62</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E49" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D50">
         <f t="shared" si="5"/>
-        <v>349.44799999999998</v>
-      </c>
-      <c r="E50">
-        <f t="shared" si="1"/>
-        <v>349.44799999999998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>63</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E50" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D51">
         <f t="shared" si="5"/>
-        <v>352.24099999999999</v>
-      </c>
-      <c r="E51">
-        <f t="shared" si="1"/>
-        <v>352.24099999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>64</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E51" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D52">
         <f t="shared" si="5"/>
-        <v>361.84399999999999</v>
-      </c>
-      <c r="E52">
-        <f t="shared" si="1"/>
-        <v>361.84399999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>65</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E52" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D53">
         <f t="shared" si="5"/>
-        <v>379.24</v>
-      </c>
-      <c r="E53">
-        <f t="shared" si="1"/>
-        <v>379.24</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>66</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E53" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D54">
         <f t="shared" si="5"/>
-        <v>391.98399999999998</v>
-      </c>
-      <c r="E54">
-        <f t="shared" si="1"/>
-        <v>391.98399999999998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>67</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E54" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D55">
         <f t="shared" si="5"/>
-        <v>371.899</v>
-      </c>
-      <c r="E55">
-        <f t="shared" si="1"/>
-        <v>371.899</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>68</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E55" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D56">
         <f t="shared" si="5"/>
-        <v>396.37700000000001</v>
-      </c>
-      <c r="E56">
-        <f t="shared" si="1"/>
-        <v>396.37700000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>69</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E56" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D57">
         <f t="shared" si="5"/>
-        <v>373.41699999999997</v>
-      </c>
-      <c r="E57">
-        <f t="shared" si="1"/>
-        <v>373.41699999999997</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>70</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E57" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D58">
         <f t="shared" si="5"/>
-        <v>355.07600000000002</v>
-      </c>
-      <c r="E58">
-        <f t="shared" si="1"/>
-        <v>355.07600000000002</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>71</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E58" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D59">
         <f t="shared" si="5"/>
-        <v>394.25200000000001</v>
-      </c>
-      <c r="E59">
-        <f t="shared" si="1"/>
-        <v>394.25200000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>72</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E59" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D60">
         <f t="shared" si="5"/>
-        <v>425.755</v>
-      </c>
-      <c r="E60">
-        <f t="shared" si="1"/>
-        <v>425.755</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>73</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E60" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D61">
         <f t="shared" si="5"/>
-        <v>446.43299999999999</v>
-      </c>
-      <c r="E61">
-        <f t="shared" si="1"/>
-        <v>446.43299999999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E61" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D62">
         <f t="shared" si="5"/>
-        <v>481.12400000000002</v>
-      </c>
-      <c r="E62">
-        <f t="shared" si="1"/>
-        <v>481.12400000000002</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E62" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D63">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -1943,7 +3275,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D64">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -2477,4 +3809,866 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56E8994F-C164-404A-97E8-1E44758D2260}">
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>2.144571</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2.0329869999999999</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1.9170039999999999</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2.2010800000000001</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2.1058110000000001</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1.986856</v>
+      </c>
+      <c r="H2" s="2">
+        <v>2.3415629999999998</v>
+      </c>
+      <c r="I2" s="2">
+        <v>2.323677</v>
+      </c>
+      <c r="J2" s="2">
+        <v>2.8115060000000001</v>
+      </c>
+      <c r="K2" s="2">
+        <v>2.7914029999999999</v>
+      </c>
+      <c r="L2" s="2">
+        <v>3.3825430000000001</v>
+      </c>
+      <c r="M2" s="2">
+        <v>4.0457400000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.73171379999999997</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.62592239999999999</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.5084362</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.43139470000000002</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.39995570000000003</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.39006079999999999</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.40731529999999999</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.44497940000000002</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.41724489999999997</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.47844039999999999</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0.54200470000000001</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0.61107540000000005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>10.419269999999999</v>
+      </c>
+      <c r="C4" s="2">
+        <v>9.1101279999999996</v>
+      </c>
+      <c r="D4" s="2">
+        <v>9.2526119999999992</v>
+      </c>
+      <c r="E4" s="2">
+        <v>8.4888089999999998</v>
+      </c>
+      <c r="F4" s="2">
+        <v>9.6159140000000001</v>
+      </c>
+      <c r="G4" s="2">
+        <v>9.9034510000000004</v>
+      </c>
+      <c r="H4" s="2">
+        <v>10.250959999999999</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9.8108699999999995</v>
+      </c>
+      <c r="J4" s="2">
+        <v>10.36229</v>
+      </c>
+      <c r="K4" s="2">
+        <v>10.62311</v>
+      </c>
+      <c r="L4" s="2">
+        <v>10.28467</v>
+      </c>
+      <c r="M4" s="2">
+        <v>11.13823</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2">
+        <v>6</v>
+      </c>
+      <c r="H6" s="2">
+        <v>7</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8</v>
+      </c>
+      <c r="J6" s="2">
+        <v>11</v>
+      </c>
+      <c r="K6" s="2">
+        <v>14</v>
+      </c>
+      <c r="L6" s="2">
+        <v>18</v>
+      </c>
+      <c r="M6" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <f>$B2/B2-1</f>
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:M7" si="0">$B2/C2-1</f>
+        <v>5.4886725788212187E-2</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>0.11870971578567402</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>-2.5673305831682702E-2</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>1.8406210243939292E-2</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>7.9379179970767932E-2</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>-8.4128421913055473E-2</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>-7.7078698975804327E-2</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>-0.23721628194995847</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>-0.23172290063455536</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>-0.36598854766960831</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>-0.46991872933011025</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <f t="shared" ref="B8:M8" si="1">$B3/B3-1</f>
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>0.16901679824847293</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>0.43914575712744286</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>0.69615852953223567</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>0.82948711569806344</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>0.87589678327071052</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>0.79643092218730782</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>0.64437679586965135</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>0.75367943382890967</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>0.52937293756965342</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="1"/>
+        <v>0.35001375449327288</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="1"/>
+        <v>0.19741982740591402</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <f t="shared" ref="B9:M9" si="2">$B4/B4-1</f>
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="2"/>
+        <v>0.1437018228503486</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="2"/>
+        <v>0.12608958421686767</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="2"/>
+        <v>0.22741246740267096</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="2"/>
+        <v>8.3544424378171334E-2</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="2"/>
+        <v>5.2084773277516927E-2</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="2"/>
+        <v>1.6418950030046009E-2</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="2"/>
+        <v>6.2012849013390214E-2</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="2"/>
+        <v>5.4987845350786824E-3</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>-1.9188354446108669E-2</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="2"/>
+        <v>1.3087439849795768E-2</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="2"/>
+        <v>-6.4548855608117406E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>6</v>
+      </c>
+      <c r="H11">
+        <v>7</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
+      </c>
+      <c r="J11">
+        <v>11</v>
+      </c>
+      <c r="K11">
+        <v>14</v>
+      </c>
+      <c r="L11">
+        <v>18</v>
+      </c>
+      <c r="M11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>5.4886725788212187E-2</v>
+      </c>
+      <c r="D12">
+        <v>0.11870971578567402</v>
+      </c>
+      <c r="E12">
+        <v>-2.5673305831682702E-2</v>
+      </c>
+      <c r="F12">
+        <v>1.8406210243939292E-2</v>
+      </c>
+      <c r="G12">
+        <v>7.9379179970767932E-2</v>
+      </c>
+      <c r="H12">
+        <v>-8.4128421913055473E-2</v>
+      </c>
+      <c r="I12">
+        <v>-7.7078698975804327E-2</v>
+      </c>
+      <c r="J12">
+        <v>-0.23721628194995847</v>
+      </c>
+      <c r="K12">
+        <v>-0.23172290063455536</v>
+      </c>
+      <c r="L12">
+        <v>-0.36598854766960831</v>
+      </c>
+      <c r="M12">
+        <v>-0.46991872933011025</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0.16901679824847293</v>
+      </c>
+      <c r="D13">
+        <v>0.43914575712744286</v>
+      </c>
+      <c r="E13">
+        <v>0.69615852953223567</v>
+      </c>
+      <c r="F13">
+        <v>0.82948711569806344</v>
+      </c>
+      <c r="G13">
+        <v>0.87589678327071052</v>
+      </c>
+      <c r="H13">
+        <v>0.79643092218730782</v>
+      </c>
+      <c r="I13">
+        <v>0.64437679586965135</v>
+      </c>
+      <c r="J13">
+        <v>0.75367943382890967</v>
+      </c>
+      <c r="K13">
+        <v>0.52937293756965342</v>
+      </c>
+      <c r="L13">
+        <v>0.35001375449327288</v>
+      </c>
+      <c r="M13">
+        <v>0.19741982740591402</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0.1437018228503486</v>
+      </c>
+      <c r="D14">
+        <v>0.12608958421686767</v>
+      </c>
+      <c r="E14">
+        <v>0.22741246740267096</v>
+      </c>
+      <c r="F14">
+        <v>8.3544424378171334E-2</v>
+      </c>
+      <c r="G14">
+        <v>5.2084773277516927E-2</v>
+      </c>
+      <c r="H14">
+        <v>1.6418950030046009E-2</v>
+      </c>
+      <c r="I14">
+        <v>6.2012849013390214E-2</v>
+      </c>
+      <c r="J14">
+        <v>5.4987845350786824E-3</v>
+      </c>
+      <c r="K14">
+        <v>-1.9188354446108669E-2</v>
+      </c>
+      <c r="L14">
+        <v>1.3087439849795768E-2</v>
+      </c>
+      <c r="M14">
+        <v>-6.4548855608117406E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>2.144571</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0.73171379999999997</v>
+      </c>
+      <c r="I17" s="2">
+        <v>10.419269999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>5.4886725788212187E-2</v>
+      </c>
+      <c r="C18">
+        <v>0.16901679824847293</v>
+      </c>
+      <c r="D18">
+        <v>0.1437018228503486</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2">
+        <v>2.0329869999999999</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0.62592239999999999</v>
+      </c>
+      <c r="I18" s="2">
+        <v>9.1101279999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>0.11870971578567402</v>
+      </c>
+      <c r="C19">
+        <v>0.43914575712744286</v>
+      </c>
+      <c r="D19">
+        <v>0.12608958421686767</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1.9170039999999999</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0.5084362</v>
+      </c>
+      <c r="I19" s="2">
+        <v>9.2526119999999992</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>4</v>
+      </c>
+      <c r="B20">
+        <v>-2.5673305831682702E-2</v>
+      </c>
+      <c r="C20">
+        <v>0.69615852953223567</v>
+      </c>
+      <c r="D20">
+        <v>0.22741246740267096</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20" s="2">
+        <v>2.2010800000000001</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0.43139470000000002</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.4888089999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>1.8406210243939292E-2</v>
+      </c>
+      <c r="C21">
+        <v>0.82948711569806344</v>
+      </c>
+      <c r="D21">
+        <v>8.3544424378171334E-2</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21" s="2">
+        <v>2.1058110000000001</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0.39995570000000003</v>
+      </c>
+      <c r="I21" s="2">
+        <v>9.6159140000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>6</v>
+      </c>
+      <c r="B22">
+        <v>7.9379179970767932E-2</v>
+      </c>
+      <c r="C22">
+        <v>0.87589678327071052</v>
+      </c>
+      <c r="D22">
+        <v>5.2084773277516927E-2</v>
+      </c>
+      <c r="F22">
+        <v>6</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1.986856</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0.39006079999999999</v>
+      </c>
+      <c r="I22" s="2">
+        <v>9.9034510000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>7</v>
+      </c>
+      <c r="B23">
+        <v>-8.4128421913055473E-2</v>
+      </c>
+      <c r="C23">
+        <v>0.79643092218730782</v>
+      </c>
+      <c r="D23">
+        <v>1.6418950030046009E-2</v>
+      </c>
+      <c r="F23">
+        <v>7</v>
+      </c>
+      <c r="G23" s="2">
+        <v>2.3415629999999998</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0.40731529999999999</v>
+      </c>
+      <c r="I23" s="2">
+        <v>10.250959999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>8</v>
+      </c>
+      <c r="B24">
+        <v>-7.7078698975804327E-2</v>
+      </c>
+      <c r="C24">
+        <v>0.64437679586965135</v>
+      </c>
+      <c r="D24">
+        <v>6.2012849013390214E-2</v>
+      </c>
+      <c r="F24">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2">
+        <v>2.323677</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0.44497940000000002</v>
+      </c>
+      <c r="I24" s="2">
+        <v>9.8108699999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>-0.23721628194995847</v>
+      </c>
+      <c r="C25">
+        <v>0.75367943382890967</v>
+      </c>
+      <c r="D25">
+        <v>5.4987845350786824E-3</v>
+      </c>
+      <c r="F25">
+        <v>11</v>
+      </c>
+      <c r="G25" s="2">
+        <v>2.8115060000000001</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0.41724489999999997</v>
+      </c>
+      <c r="I25" s="2">
+        <v>10.36229</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>14</v>
+      </c>
+      <c r="B26">
+        <v>-0.23172290063455536</v>
+      </c>
+      <c r="C26">
+        <v>0.52937293756965342</v>
+      </c>
+      <c r="D26">
+        <v>-1.9188354446108669E-2</v>
+      </c>
+      <c r="F26">
+        <v>14</v>
+      </c>
+      <c r="G26" s="2">
+        <v>2.7914029999999999</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0.47844039999999999</v>
+      </c>
+      <c r="I26" s="2">
+        <v>10.62311</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>18</v>
+      </c>
+      <c r="B27">
+        <v>-0.36598854766960831</v>
+      </c>
+      <c r="C27">
+        <v>0.35001375449327288</v>
+      </c>
+      <c r="D27">
+        <v>1.3087439849795768E-2</v>
+      </c>
+      <c r="F27">
+        <v>18</v>
+      </c>
+      <c r="G27" s="2">
+        <v>3.3825430000000001</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0.54200470000000001</v>
+      </c>
+      <c r="I27" s="2">
+        <v>10.28467</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>22</v>
+      </c>
+      <c r="B28">
+        <v>-0.46991872933011025</v>
+      </c>
+      <c r="C28">
+        <v>0.19741982740591402</v>
+      </c>
+      <c r="D28">
+        <v>-6.4548855608117406E-2</v>
+      </c>
+      <c r="F28">
+        <v>22</v>
+      </c>
+      <c r="G28" s="2">
+        <v>4.0457400000000003</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0.61107540000000005</v>
+      </c>
+      <c r="I28" s="2">
+        <v>11.13823</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>